--- a/IG/7日版/AI Native-提案_IG.xlsx
+++ b/IG/7日版/AI Native-提案_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A9026B-3E6F-4202-BB0C-2476AC2CFDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594AD665-5B04-4BEF-8C5D-A521CBA74553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="168">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -347,16 +347,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>オリエンテーション用資材</t>
-    <rPh sb="9" eb="10">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シザイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>AI-01</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -382,15 +372,6 @@
   <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>・教材のダウンロード
-・本科目の概要説明
-　科目の位置づけや目的、全体スケジュールの説明</t>
-    <rPh sb="1" eb="3">
-      <t>キョウザイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -417,14 +398,6 @@
   <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【AI Native提案企画研修】研修にあたって.pptx</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【AI Native提案企画研修】提案書サンプル.pptx</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1610,19 +1583,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>【AI Native提案企画研修】提案演習の概要.pptx</t>
-    <rPh sb="17" eb="19">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エンシュウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ガイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>提案資料を指定の場所に提出することを説明する。</t>
     <rPh sb="0" eb="2">
       <t>テイアン</t>
@@ -1789,6 +1749,27 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-提案】研修の概要.pptx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-提案】提案書サンプル.pptx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-提案】研修にあたって.pptx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・教材のダウンロード
+・本科目の概要説明
+　科目の位置づけや目的、全体の説明</t>
+    <rPh sb="1" eb="3">
+      <t>キョウザイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2238,7 +2219,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2335,9 +2316,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2554,6 +2532,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2563,15 +2568,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2580,24 +2576,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2975,15 +2953,15 @@
     </row>
     <row r="2" spans="1:7" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="91" t="str">
+      <c r="B2" s="90" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案_IG」</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
     </row>
     <row r="3" spans="1:7" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -2996,10 +2974,10 @@
     </row>
     <row r="4" spans="1:7" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3007,8 +2985,8 @@
     </row>
     <row r="5" spans="1:7" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="94"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -3019,10 +2997,10 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:7" ht="16.2">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96"/>
+      <c r="C7" s="95"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
@@ -3039,450 +3017,450 @@
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A10" s="34">
+      <c r="A10" s="33">
         <v>0.39583333333333331</v>
       </c>
       <c r="B10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="57" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="36"/>
-      <c r="B11" s="53">
+      <c r="A11" s="35"/>
+      <c r="B11" s="52">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="56" t="str">
+      <c r="C11" s="55" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="52">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="53">
+      <c r="E11" s="77"/>
+      <c r="F11" s="52">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="78" t="str">
+      <c r="G11" s="77" t="str">
         <f>master!B42</f>
         <v>提案の実施</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="34">
+      <c r="A12" s="33">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="74">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C12" s="56" t="str">
+      <c r="C12" s="55" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="79"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="78"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="35"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="79"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="78"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="35"/>
-      <c r="B14" s="53">
+      <c r="A14" s="34"/>
+      <c r="B14" s="52">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="56" t="str">
+      <c r="C14" s="55" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="79"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="78"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="36"/>
-      <c r="B15" s="88" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="84"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="79"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="78"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="52">
+      <c r="A16" s="51">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="53">
+      <c r="B16" s="52">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="90" t="str">
+      <c r="C16" s="89" t="str">
         <f>master!B32</f>
         <v>演習の全体像</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="79"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="78"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="49"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="86" t="str">
+      <c r="A17" s="48"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="85" t="str">
         <f>master!B35</f>
         <v>提案資料の作成</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="79"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="78"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="49"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="79"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="78"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="85"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="79"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="78"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="52">
+      <c r="A20" s="51">
         <v>0.5</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="79"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="78"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="49"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="77"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="76"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="35"/>
-      <c r="B22" s="35">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="34">
         <v>0.52083333333333337</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="34">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="58" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="36"/>
-      <c r="B23" s="35" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="35" t="s">
+      <c r="C23" s="59"/>
+      <c r="D23" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="60"/>
-      <c r="F23" s="35" t="s">
+      <c r="E23" s="59"/>
+      <c r="F23" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="60"/>
+      <c r="G23" s="59"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="34">
+      <c r="A24" s="33">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="60"/>
-      <c r="D24" s="35" t="s">
+      <c r="C24" s="59"/>
+      <c r="D24" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="35" t="s">
+      <c r="E24" s="59"/>
+      <c r="F24" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="60"/>
+      <c r="G24" s="59"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="36" t="s">
+      <c r="C25" s="60"/>
+      <c r="D25" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="36" t="s">
+      <c r="E25" s="60"/>
+      <c r="F25" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="61"/>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="35"/>
-      <c r="B26" s="37">
+      <c r="A26" s="34"/>
+      <c r="B26" s="36">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="78"/>
-      <c r="D26" s="37">
+      <c r="C26" s="77"/>
+      <c r="D26" s="36">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="37">
+      <c r="E26" s="77"/>
+      <c r="F26" s="36">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="78" t="str">
+      <c r="G26" s="77" t="str">
         <f>master!B47</f>
         <v>提案の改善</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="36"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="79"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="78"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="34">
+      <c r="A28" s="33">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="79"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="78"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="35"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="48"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="47"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="35"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="48"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="47"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="36"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="48"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="47"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="52">
+      <c r="A32" s="51">
         <v>0.625</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="48"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="47"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="49"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="48"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="47"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="49"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="48"/>
+      <c r="A34" s="48"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="47"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="36"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="48"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="47"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="34">
+      <c r="A36" s="33">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="48"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="47"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="35"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="48"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="47"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="35"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="48"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="47"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="35"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="48"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="37">
+      <c r="A40" s="36">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B40" s="39"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="48"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="35"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="39">
+      <c r="A41" s="34"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="38">
         <v>0.71875</v>
       </c>
-      <c r="G41" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="H41" s="50"/>
+      <c r="G41" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="49"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="48"/>
+      <c r="A42" s="38"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="47"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A43" s="38"/>
-      <c r="B43" s="71">
+      <c r="A43" s="37"/>
+      <c r="B43" s="70">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="71">
+      <c r="C43" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="70">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="71">
+      <c r="E43" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="70">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="H43" s="49"/>
+      <c r="G43" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" s="48"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
@@ -3546,10 +3524,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="100"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3560,16 +3538,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3584,10 +3562,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="102"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -3602,16 +3580,16 @@
         <v>17</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="33" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="32" t="s">
         <v>18</v>
       </c>
       <c r="K8" s="6"/>
@@ -3619,67 +3597,67 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="103" t="s">
+      <c r="H10" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="104"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="103"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="99"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="97" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="80" t="s">
-        <v>41</v>
+        <v>111</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="79" t="s">
+        <v>39</v>
       </c>
       <c r="H12" s="19"/>
-      <c r="I12" s="46" t="s">
+      <c r="I12" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="51">
+      <c r="J12" s="50">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K12" s="19"/>
@@ -3689,21 +3667,21 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="97" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="80" t="s">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="79" t="s">
+        <v>113</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="46" t="s">
+      <c r="I13" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="50">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="19"/>
@@ -3713,21 +3691,21 @@
       <c r="A14" s="10"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="97" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="80" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="D14" s="96" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="79" t="s">
+        <v>113</v>
       </c>
       <c r="H14" s="19"/>
-      <c r="I14" s="46" t="s">
+      <c r="I14" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="51">
+      <c r="J14" s="50">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K14" s="19"/>
@@ -3820,12 +3798,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3836,16 +3814,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -3865,17 +3843,17 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="102"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="44"/>
+      <c r="I7" s="43"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
@@ -3884,19 +3862,19 @@
     </row>
     <row r="8" spans="1:14">
       <c r="B8" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="33" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="32" t="s">
         <v>18</v>
       </c>
       <c r="K8" s="6"/>
@@ -3906,19 +3884,19 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="33" t="s">
+      <c r="E9" s="40"/>
+      <c r="F9" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="32" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="6"/>
@@ -3928,19 +3906,19 @@
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="33" t="s">
+      <c r="E10" s="40"/>
+      <c r="F10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="32" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
@@ -3950,28 +3928,28 @@
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1">
       <c r="A12" s="10"/>
-      <c r="B12" s="99" t="s">
+      <c r="B12" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="99" t="s">
+      <c r="D12" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99" t="s">
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="98" t="s">
+      <c r="H12" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="117" t="s">
+      <c r="I12" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="118"/>
-      <c r="K12" s="98" t="s">
+      <c r="J12" s="111"/>
+      <c r="K12" s="97" t="s">
         <v>32</v>
       </c>
       <c r="L12" s="6"/>
@@ -3980,1361 +3958,1357 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="10"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="98"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="97"/>
       <c r="I13" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="99"/>
+      <c r="K13" s="98"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" ht="63">
       <c r="A14" s="10"/>
-      <c r="B14" s="73" t="str">
+      <c r="B14" s="72" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
-      <c r="C14" s="47" t="str">
+      <c r="C14" s="46" t="str">
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D14" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="115"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="47" t="s">
-        <v>81</v>
+      <c r="D14" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="108"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="46" t="s">
+        <v>77</v>
       </c>
       <c r="H14" s="12"/>
-      <c r="I14" s="45" t="s">
+      <c r="I14" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="43">
+      <c r="J14" s="42">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K14" s="40"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="111" t="str">
+      <c r="B15" s="116" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="C15" s="47" t="str">
+      <c r="C15" s="46" t="str">
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D15" s="114" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="47" t="s">
-        <v>81</v>
+      <c r="D15" s="107" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="108"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="46" t="s">
+        <v>77</v>
       </c>
       <c r="H15" s="12"/>
-      <c r="I15" s="45" t="s">
+      <c r="I15" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="42">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K15" s="40"/>
+      <c r="K15" s="39"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="163.80000000000001">
       <c r="A16" s="11"/>
-      <c r="B16" s="112"/>
-      <c r="C16" s="47" t="str">
+      <c r="B16" s="117"/>
+      <c r="C16" s="46" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D16" s="114" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="115"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="47" t="s">
-        <v>112</v>
+      <c r="D16" s="107" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="108"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="46" t="s">
+        <v>108</v>
       </c>
       <c r="H16" s="12"/>
-      <c r="I16" s="45" t="s">
+      <c r="I16" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="42">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K16" s="40"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="112"/>
-      <c r="C17" s="47" t="str">
+      <c r="B17" s="117"/>
+      <c r="C17" s="46" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D17" s="114" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="115"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="47" t="s">
-        <v>36</v>
+      <c r="D17" s="107" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="46" t="s">
+        <v>35</v>
       </c>
       <c r="H17" s="12"/>
-      <c r="I17" s="45" t="s">
+      <c r="I17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K17" s="40"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="151.19999999999999">
       <c r="A18" s="11"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="47" t="str">
+      <c r="B18" s="117"/>
+      <c r="C18" s="46" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D18" s="114" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="47" t="s">
-        <v>43</v>
+      <c r="D18" s="107" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="108"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="46" t="s">
+        <v>41</v>
       </c>
       <c r="H18" s="12"/>
-      <c r="I18" s="45" t="s">
+      <c r="I18" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="42">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K18" s="40"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" ht="252">
       <c r="A19" s="11"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="47" t="str">
+      <c r="B19" s="117"/>
+      <c r="C19" s="46" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="47" t="s">
-        <v>45</v>
+      <c r="D19" s="107" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="108"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="46" t="s">
+        <v>43</v>
       </c>
       <c r="H19" s="12"/>
-      <c r="I19" s="45" t="s">
+      <c r="I19" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="43">
+      <c r="J19" s="42">
         <v>0</v>
       </c>
-      <c r="K19" s="40"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="112"/>
-      <c r="C20" s="47" t="str">
+      <c r="B20" s="117"/>
+      <c r="C20" s="46" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D20" s="114" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="47" t="s">
-        <v>44</v>
+      <c r="D20" s="107" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="108"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="46" t="s">
+        <v>42</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="43">
+      <c r="J20" s="42">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K20" s="40"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="63">
       <c r="A21" s="11"/>
-      <c r="B21" s="112"/>
-      <c r="C21" s="47" t="str">
+      <c r="B21" s="117"/>
+      <c r="C21" s="46" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D21" s="114" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="47" t="s">
-        <v>81</v>
+      <c r="D21" s="107" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="108"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="46" t="s">
+        <v>77</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="45" t="s">
+      <c r="I21" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="43">
+      <c r="J21" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K21" s="40"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="75.599999999999994">
       <c r="A22" s="11"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="47" t="str">
+      <c r="B22" s="117"/>
+      <c r="C22" s="46" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D22" s="114" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="115"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="47" t="s">
-        <v>37</v>
+      <c r="D22" s="107" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="H22" s="12"/>
-      <c r="I22" s="45" t="s">
+      <c r="I22" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="43">
+      <c r="J22" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K22" s="40"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="47" t="str">
+      <c r="B23" s="117"/>
+      <c r="C23" s="46" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D23" s="114" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="116"/>
-      <c r="G23" s="47" t="s">
-        <v>37</v>
+      <c r="D23" s="107" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="108"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="H23" s="12"/>
-      <c r="I23" s="45" t="s">
+      <c r="I23" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="43">
+      <c r="J23" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K23" s="40"/>
+      <c r="K23" s="39"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="113.4">
       <c r="A24" s="11"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="47" t="str">
+      <c r="B24" s="117"/>
+      <c r="C24" s="46" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D24" s="114" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" s="115"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="47" t="s">
-        <v>38</v>
+      <c r="D24" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="108"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="46" t="s">
+        <v>37</v>
       </c>
       <c r="H24" s="12"/>
-      <c r="I24" s="45" t="s">
+      <c r="I24" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="43">
+      <c r="J24" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K24" s="40"/>
+      <c r="K24" s="39"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" ht="88.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="112"/>
-      <c r="C25" s="47" t="str">
+      <c r="B25" s="117"/>
+      <c r="C25" s="46" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D25" s="114" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="47" t="s">
-        <v>39</v>
+      <c r="D25" s="107" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="46" t="s">
+        <v>38</v>
       </c>
       <c r="H25" s="12"/>
-      <c r="I25" s="45" t="s">
+      <c r="I25" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="43">
+      <c r="J25" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K25" s="40"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="113"/>
-      <c r="C26" s="47" t="str">
+      <c r="B26" s="118"/>
+      <c r="C26" s="46" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D26" s="114" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="115"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="47" t="s">
-        <v>38</v>
+      <c r="D26" s="107" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="108"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="46" t="s">
+        <v>37</v>
       </c>
       <c r="H26" s="12"/>
-      <c r="I26" s="45" t="s">
+      <c r="I26" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="43">
+      <c r="J26" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K26" s="40"/>
+      <c r="K26" s="39"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
     <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="111" t="str">
+      <c r="B27" s="116" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
-      <c r="C27" s="47" t="str">
+      <c r="C27" s="46" t="str">
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D27" s="114" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="115"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="47" t="s">
-        <v>96</v>
+      <c r="D27" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="H27" s="12"/>
-      <c r="I27" s="45" t="s">
+      <c r="I27" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="43">
+      <c r="J27" s="42">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K27" s="40"/>
+      <c r="K27" s="39"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
     <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="112"/>
-      <c r="C28" s="47" t="str">
+      <c r="B28" s="117"/>
+      <c r="C28" s="46" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D28" s="114" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="115"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="47" t="s">
-        <v>77</v>
+      <c r="D28" s="107" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="46" t="s">
+        <v>73</v>
       </c>
       <c r="H28" s="12"/>
-      <c r="I28" s="45" t="s">
+      <c r="I28" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="43">
+      <c r="J28" s="42">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K28" s="40"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="112"/>
-      <c r="C29" s="47" t="str">
+      <c r="B29" s="117"/>
+      <c r="C29" s="46" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D29" s="114" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="115"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="47" t="s">
-        <v>77</v>
+      <c r="D29" s="107" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="46" t="s">
+        <v>73</v>
       </c>
       <c r="H29" s="12"/>
-      <c r="I29" s="45" t="s">
+      <c r="I29" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="43">
+      <c r="J29" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K29" s="40"/>
+      <c r="K29" s="39"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="112"/>
-      <c r="C30" s="47" t="str">
+      <c r="B30" s="117"/>
+      <c r="C30" s="46" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D30" s="114" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="115"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="47" t="s">
-        <v>77</v>
+      <c r="D30" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="108"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="46" t="s">
+        <v>73</v>
       </c>
       <c r="H30" s="12"/>
-      <c r="I30" s="45" t="s">
+      <c r="I30" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="43">
+      <c r="J30" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K30" s="40"/>
+      <c r="K30" s="39"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="63">
       <c r="A31" s="11"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="47" t="str">
+      <c r="B31" s="117"/>
+      <c r="C31" s="46" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D31" s="114" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" s="115"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="47" t="s">
-        <v>97</v>
+      <c r="D31" s="107" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="108"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="H31" s="12"/>
-      <c r="I31" s="45" t="s">
+      <c r="I31" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="43">
+      <c r="J31" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K31" s="40"/>
+      <c r="K31" s="39"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="112"/>
-      <c r="C32" s="47" t="str">
+      <c r="B32" s="117"/>
+      <c r="C32" s="46" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D32" s="114" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" s="115"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="47" t="s">
-        <v>96</v>
+      <c r="D32" s="107" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="108"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="H32" s="12"/>
-      <c r="I32" s="45" t="s">
+      <c r="I32" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="43">
+      <c r="J32" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K32" s="40"/>
+      <c r="K32" s="39"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="112"/>
-      <c r="C33" s="47" t="str">
+      <c r="B33" s="117"/>
+      <c r="C33" s="46" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D33" s="114" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="115"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="47" t="s">
-        <v>96</v>
+      <c r="D33" s="107" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="108"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="H33" s="12"/>
-      <c r="I33" s="45" t="s">
+      <c r="I33" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="43">
+      <c r="J33" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K33" s="40"/>
+      <c r="K33" s="39"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="63">
       <c r="A34" s="11"/>
-      <c r="B34" s="112"/>
-      <c r="C34" s="47" t="str">
+      <c r="B34" s="117"/>
+      <c r="C34" s="46" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D34" s="114" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34" s="115"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="47" t="s">
-        <v>97</v>
+      <c r="D34" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="108"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="H34" s="12"/>
-      <c r="I34" s="45" t="s">
+      <c r="I34" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="43">
+      <c r="J34" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K34" s="40"/>
+      <c r="K34" s="39"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
     <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="112"/>
-      <c r="C35" s="47" t="str">
+      <c r="B35" s="117"/>
+      <c r="C35" s="46" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D35" s="114" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="115"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="47" t="s">
-        <v>77</v>
+      <c r="D35" s="107" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="108"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="46" t="s">
+        <v>73</v>
       </c>
       <c r="H35" s="12"/>
-      <c r="I35" s="45" t="s">
+      <c r="I35" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="43">
+      <c r="J35" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K35" s="40"/>
+      <c r="K35" s="39"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="112"/>
-      <c r="C36" s="47" t="str">
+      <c r="B36" s="117"/>
+      <c r="C36" s="46" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D36" s="114" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="47" t="s">
-        <v>96</v>
+      <c r="D36" s="107" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="108"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="H36" s="12"/>
-      <c r="I36" s="45" t="s">
+      <c r="I36" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J36" s="43">
+      <c r="J36" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K36" s="40"/>
+      <c r="K36" s="39"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" ht="63">
       <c r="A37" s="11"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="47" t="str">
+      <c r="B37" s="117"/>
+      <c r="C37" s="46" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D37" s="114" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="115"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="47" t="s">
-        <v>97</v>
+      <c r="D37" s="107" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="108"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="H37" s="12"/>
-      <c r="I37" s="45" t="s">
+      <c r="I37" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J37" s="43">
+      <c r="J37" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K37" s="40"/>
+      <c r="K37" s="39"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="112"/>
-      <c r="C38" s="47" t="str">
+      <c r="B38" s="117"/>
+      <c r="C38" s="46" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D38" s="114" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" s="115"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="47" t="s">
-        <v>97</v>
+      <c r="D38" s="107" t="s">
+        <v>102</v>
+      </c>
+      <c r="E38" s="108"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="H38" s="12"/>
-      <c r="I38" s="45" t="s">
+      <c r="I38" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="43">
+      <c r="J38" s="42">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K38" s="40"/>
+      <c r="K38" s="39"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="113"/>
-      <c r="C39" s="47" t="str">
+      <c r="B39" s="118"/>
+      <c r="C39" s="46" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D39" s="114" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="115"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="47" t="s">
-        <v>96</v>
+      <c r="D39" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="108"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="H39" s="12"/>
-      <c r="I39" s="45" t="s">
+      <c r="I39" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="43">
+      <c r="J39" s="42">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K39" s="40"/>
+      <c r="K39" s="39"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="105" t="str">
+      <c r="B40" s="113" t="str">
         <f>master!B32</f>
         <v>演習の全体像</v>
       </c>
-      <c r="C40" s="64" t="str">
+      <c r="C40" s="63" t="str">
         <f>master!C32</f>
         <v>全体像について</v>
       </c>
-      <c r="D40" s="108" t="s">
-        <v>163</v>
-      </c>
-      <c r="E40" s="109"/>
-      <c r="F40" s="110"/>
-      <c r="G40" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="H40" s="65"/>
-      <c r="I40" s="66" t="s">
+      <c r="D40" s="104" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="105"/>
+      <c r="F40" s="106"/>
+      <c r="G40" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" s="64"/>
+      <c r="I40" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J40" s="67">
+      <c r="J40" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K40" s="68"/>
+      <c r="K40" s="67"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
     <row r="41" spans="1:14" ht="138.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="106"/>
-      <c r="C41" s="64" t="str">
+      <c r="B41" s="114"/>
+      <c r="C41" s="63" t="str">
         <f>master!C33</f>
         <v>提案資料について</v>
       </c>
-      <c r="D41" s="108" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" s="109"/>
-      <c r="F41" s="110"/>
-      <c r="G41" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="H41" s="65"/>
-      <c r="I41" s="66" t="s">
+      <c r="D41" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" s="105"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="64"/>
+      <c r="I41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="67">
+      <c r="J41" s="66">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K41" s="68"/>
+      <c r="K41" s="67"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="126">
       <c r="A42" s="11"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="64" t="str">
+      <c r="B42" s="115"/>
+      <c r="C42" s="63" t="str">
         <f>master!C34</f>
         <v>提案資料の提出ついて</v>
       </c>
-      <c r="D42" s="108" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" s="109"/>
-      <c r="F42" s="110"/>
-      <c r="G42" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="H42" s="64"/>
-      <c r="I42" s="66" t="s">
+      <c r="D42" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="105"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="63"/>
+      <c r="I42" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="67">
+      <c r="J42" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K42" s="68"/>
+      <c r="K42" s="67"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="105" t="str">
+      <c r="B43" s="113" t="str">
         <f>master!B35</f>
         <v>提案資料の作成</v>
       </c>
-      <c r="C43" s="64" t="str">
+      <c r="C43" s="63" t="str">
         <f>master!C35</f>
         <v>提案テーマの検討</v>
       </c>
-      <c r="D43" s="108" t="s">
-        <v>141</v>
-      </c>
-      <c r="E43" s="109"/>
-      <c r="F43" s="110"/>
-      <c r="G43" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43" s="65"/>
-      <c r="I43" s="66" t="s">
+      <c r="D43" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" s="105"/>
+      <c r="F43" s="106"/>
+      <c r="G43" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="H43" s="64"/>
+      <c r="I43" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="67">
+      <c r="J43" s="66">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K43" s="68"/>
+      <c r="K43" s="67"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="106"/>
-      <c r="C44" s="64" t="str">
+      <c r="B44" s="114"/>
+      <c r="C44" s="63" t="str">
         <f>master!C36</f>
         <v>提案テーマの意見交換</v>
       </c>
-      <c r="D44" s="108" t="s">
-        <v>142</v>
-      </c>
-      <c r="E44" s="109"/>
-      <c r="F44" s="110"/>
-      <c r="G44" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="H44" s="65"/>
-      <c r="I44" s="66" t="s">
+      <c r="D44" s="104" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="105"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="67">
+      <c r="J44" s="66">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K44" s="68"/>
+      <c r="K44" s="67"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="75.599999999999994">
       <c r="A45" s="11"/>
-      <c r="B45" s="106"/>
-      <c r="C45" s="64" t="str">
+      <c r="B45" s="114"/>
+      <c r="C45" s="63" t="str">
         <f>master!C37</f>
         <v>提案テーマの調査</v>
       </c>
-      <c r="D45" s="108" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" s="109"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="64" t="s">
+      <c r="D45" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="H45" s="65"/>
-      <c r="I45" s="66" t="s">
+      <c r="E45" s="105"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="H45" s="64"/>
+      <c r="I45" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="67">
+      <c r="J45" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K45" s="68"/>
+      <c r="K45" s="67"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="106"/>
-      <c r="C46" s="64" t="str">
+      <c r="B46" s="114"/>
+      <c r="C46" s="63" t="str">
         <f>master!C38</f>
         <v>提案内容の具体化</v>
       </c>
-      <c r="D46" s="108" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" s="109"/>
-      <c r="F46" s="110"/>
-      <c r="G46" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="H46" s="65"/>
-      <c r="I46" s="66" t="s">
+      <c r="D46" s="104" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="105"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="67">
+      <c r="J46" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K46" s="68"/>
+      <c r="K46" s="67"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="151.19999999999999">
       <c r="A47" s="11"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="64" t="str">
+      <c r="B47" s="114"/>
+      <c r="C47" s="63" t="str">
         <f>master!C39</f>
         <v>提案資料の作成</v>
       </c>
-      <c r="D47" s="108" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" s="109"/>
-      <c r="F47" s="110"/>
-      <c r="G47" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="H47" s="65"/>
-      <c r="I47" s="66" t="s">
+      <c r="D47" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="105"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="67">
+      <c r="J47" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K47" s="68"/>
+      <c r="K47" s="67"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
     <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="106"/>
-      <c r="C48" s="64" t="str">
+      <c r="B48" s="114"/>
+      <c r="C48" s="63" t="str">
         <f>master!C40</f>
         <v>提案資料の提出</v>
       </c>
-      <c r="D48" s="108" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" s="109"/>
-      <c r="F48" s="110"/>
-      <c r="G48" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H48" s="65"/>
-      <c r="I48" s="66" t="s">
+      <c r="D48" s="104" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="105"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="67">
+      <c r="J48" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K48" s="68"/>
+      <c r="K48" s="67"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="25.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="64" t="str">
+      <c r="B49" s="114"/>
+      <c r="C49" s="63" t="str">
         <f>master!C41</f>
         <v>演習の実施</v>
       </c>
-      <c r="D49" s="108"/>
-      <c r="E49" s="109"/>
-      <c r="F49" s="110"/>
-      <c r="G49" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H49" s="65"/>
-      <c r="I49" s="66" t="s">
+      <c r="D49" s="104"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H49" s="64"/>
+      <c r="I49" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="K49" s="68"/>
+      <c r="J49" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="67"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="105" t="str">
+      <c r="B50" s="113" t="str">
         <f>master!B42</f>
         <v>提案の実施</v>
       </c>
-      <c r="C50" s="64" t="str">
+      <c r="C50" s="63" t="str">
         <f>master!C42</f>
         <v>提案の実施の説明</v>
       </c>
-      <c r="D50" s="108" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="109"/>
-      <c r="F50" s="110"/>
-      <c r="G50" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="H50" s="65"/>
-      <c r="I50" s="66" t="s">
+      <c r="D50" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="E50" s="105"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="64"/>
+      <c r="I50" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="67">
+      <c r="J50" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K50" s="68"/>
+      <c r="K50" s="67"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="25.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="106"/>
-      <c r="C51" s="64" t="str">
+      <c r="B51" s="114"/>
+      <c r="C51" s="63" t="str">
         <f>master!C43</f>
         <v>発表順の決定</v>
       </c>
-      <c r="D51" s="108" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" s="109"/>
-      <c r="F51" s="110"/>
-      <c r="G51" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H51" s="65"/>
-      <c r="I51" s="66" t="s">
+      <c r="D51" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="105"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H51" s="64"/>
+      <c r="I51" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J51" s="67">
+      <c r="J51" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K51" s="68"/>
+      <c r="K51" s="67"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="25.2">
       <c r="A52" s="11"/>
-      <c r="B52" s="106"/>
-      <c r="C52" s="64" t="str">
+      <c r="B52" s="114"/>
+      <c r="C52" s="63" t="str">
         <f>master!C44</f>
         <v>提案の実施</v>
       </c>
-      <c r="D52" s="108" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="110"/>
-      <c r="G52" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H52" s="65"/>
-      <c r="I52" s="66" t="s">
+      <c r="D52" s="104" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="105"/>
+      <c r="F52" s="106"/>
+      <c r="G52" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="64"/>
+      <c r="I52" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J52" s="67">
+      <c r="J52" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K52" s="68"/>
+      <c r="K52" s="67"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="25.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="106"/>
-      <c r="C53" s="64" t="str">
+      <c r="B53" s="114"/>
+      <c r="C53" s="63" t="str">
         <f>master!C45</f>
         <v>提案のフィードバック</v>
       </c>
-      <c r="D53" s="108" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" s="109"/>
-      <c r="F53" s="110"/>
-      <c r="G53" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H53" s="65"/>
-      <c r="I53" s="66" t="s">
+      <c r="D53" s="104" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="105"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H53" s="64"/>
+      <c r="I53" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J53" s="67">
+      <c r="J53" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K53" s="68"/>
+      <c r="K53" s="67"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="64" t="str">
+      <c r="B54" s="115"/>
+      <c r="C54" s="63" t="str">
         <f>master!C46</f>
         <v>演習の実施</v>
       </c>
-      <c r="D54" s="108"/>
-      <c r="E54" s="109"/>
-      <c r="F54" s="110"/>
-      <c r="G54" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H54" s="65"/>
-      <c r="I54" s="66" t="s">
+      <c r="D54" s="104"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H54" s="64"/>
+      <c r="I54" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="K54" s="68"/>
+      <c r="J54" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="67"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="113.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="105" t="str">
+      <c r="B55" s="113" t="str">
         <f>master!B47</f>
         <v>提案の改善</v>
       </c>
-      <c r="C55" s="64" t="str">
+      <c r="C55" s="63" t="str">
         <f>master!C47</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D55" s="108" t="s">
-        <v>151</v>
-      </c>
-      <c r="E55" s="109"/>
-      <c r="F55" s="110"/>
-      <c r="G55" s="64" t="s">
-        <v>78</v>
-      </c>
-      <c r="H55" s="65"/>
-      <c r="I55" s="66" t="s">
+      <c r="D55" s="104" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="105"/>
+      <c r="F55" s="106"/>
+      <c r="G55" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="H55" s="64"/>
+      <c r="I55" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J55" s="67">
+      <c r="J55" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K55" s="68"/>
+      <c r="K55" s="67"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="106"/>
-      <c r="C56" s="64" t="str">
+      <c r="B56" s="114"/>
+      <c r="C56" s="63" t="str">
         <f>master!C48</f>
         <v>フィードバック内容の整理</v>
       </c>
-      <c r="D56" s="108" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" s="109"/>
-      <c r="F56" s="110"/>
-      <c r="G56" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H56" s="65"/>
-      <c r="I56" s="66" t="s">
+      <c r="D56" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" s="105"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="64"/>
+      <c r="I56" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J56" s="67">
+      <c r="J56" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K56" s="68"/>
+      <c r="K56" s="67"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="25.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="106"/>
-      <c r="C57" s="64" t="str">
+      <c r="B57" s="114"/>
+      <c r="C57" s="63" t="str">
         <f>master!C49</f>
         <v>提案資料の修正</v>
       </c>
-      <c r="D57" s="108" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="109"/>
-      <c r="F57" s="110"/>
-      <c r="G57" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H57" s="65"/>
-      <c r="I57" s="66" t="s">
+      <c r="D57" s="104" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" s="105"/>
+      <c r="F57" s="106"/>
+      <c r="G57" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" s="64"/>
+      <c r="I57" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="67">
+      <c r="J57" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K57" s="68"/>
+      <c r="K57" s="67"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="25.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="106"/>
-      <c r="C58" s="64" t="str">
+      <c r="B58" s="114"/>
+      <c r="C58" s="63" t="str">
         <f>master!C50</f>
         <v>提案資料の確認</v>
       </c>
-      <c r="D58" s="108" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" s="109"/>
-      <c r="F58" s="110"/>
-      <c r="G58" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H58" s="65"/>
-      <c r="I58" s="66" t="s">
+      <c r="D58" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" s="105"/>
+      <c r="F58" s="106"/>
+      <c r="G58" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H58" s="64"/>
+      <c r="I58" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J58" s="67">
+      <c r="J58" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K58" s="68"/>
+      <c r="K58" s="67"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="106"/>
-      <c r="C59" s="64" t="str">
+      <c r="B59" s="114"/>
+      <c r="C59" s="63" t="str">
         <f>master!C51</f>
         <v>提案資料の提出</v>
       </c>
-      <c r="D59" s="108" t="s">
-        <v>160</v>
-      </c>
-      <c r="E59" s="109"/>
-      <c r="F59" s="110"/>
-      <c r="G59" s="64" t="s">
-        <v>159</v>
-      </c>
-      <c r="H59" s="65"/>
-      <c r="I59" s="66" t="s">
+      <c r="D59" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" s="105"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="64"/>
+      <c r="I59" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J59" s="67">
+      <c r="J59" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K59" s="68"/>
+      <c r="K59" s="67"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="106"/>
-      <c r="C60" s="64" t="str">
+      <c r="B60" s="114"/>
+      <c r="C60" s="63" t="str">
         <f>master!C52</f>
         <v>最終発表の準備</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H60" s="65"/>
-      <c r="I60" s="66" t="s">
+      <c r="D60" s="104"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H60" s="64"/>
+      <c r="I60" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J60" s="67">
+      <c r="J60" s="66">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K60" s="68"/>
+      <c r="K60" s="67"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="107"/>
-      <c r="C61" s="64" t="str">
+      <c r="B61" s="115"/>
+      <c r="C61" s="63" t="str">
         <f>master!C53</f>
         <v>演習の実施</v>
       </c>
-      <c r="D61" s="108"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="110"/>
-      <c r="G61" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="H61" s="65"/>
-      <c r="I61" s="66" t="s">
+      <c r="D61" s="104"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="106"/>
+      <c r="G61" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H61" s="64"/>
+      <c r="I61" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J61" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="K61" s="68"/>
+      <c r="J61" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="K61" s="67"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="B55:B61"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B15:B26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B27:B39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D40:F40"/>
@@ -5351,28 +5325,32 @@
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="B15:B26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B27:B39"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="B55:B61"/>
-    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D56:F56"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5405,291 +5383,291 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="61" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="69" t="s">
-        <v>110</v>
+        <v>97</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="68" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" s="68" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="C21" s="68" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" s="68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="C23" s="68" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
-      <c r="C20" s="69" t="s">
+    <row r="24" spans="2:3">
+      <c r="C24" s="68" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="C21" s="69" t="s">
+    <row r="25" spans="2:3">
+      <c r="C25" s="69" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="69" t="s">
+    <row r="26" spans="2:3">
+      <c r="C26" s="68" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
-      <c r="C23" s="69" t="s">
+    <row r="27" spans="2:3">
+      <c r="C27" s="68" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
-      <c r="C24" s="69" t="s">
+    <row r="28" spans="2:3">
+      <c r="C28" s="68" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
-      <c r="C25" s="70" t="s">
+    <row r="29" spans="2:3">
+      <c r="C29" s="68" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="69" t="s">
+    <row r="30" spans="2:3">
+      <c r="C30" s="68" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
-      <c r="C27" s="69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="69" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="C29" s="69" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="C30" s="69" t="s">
-        <v>73</v>
-      </c>
-    </row>
     <row r="31" spans="2:3">
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>161</v>
-      </c>
-      <c r="C32" s="69" t="s">
-        <v>162</v>
+        <v>156</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="69" t="s">
-        <v>150</v>
+      <c r="C33" s="68" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="69" t="s">
-        <v>164</v>
+      <c r="C34" s="68" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" s="69" t="s">
-        <v>124</v>
+        <v>131</v>
+      </c>
+      <c r="C35" s="68" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="C36" s="69" t="s">
-        <v>125</v>
+      <c r="C36" s="68" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="2:3">
-      <c r="C37" s="69" t="s">
-        <v>127</v>
+      <c r="C37" s="68" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="69" t="s">
-        <v>145</v>
+      <c r="C41" s="68" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" s="69" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" s="69" t="s">
-        <v>137</v>
+      <c r="C43" s="68" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="2:3">
-      <c r="C44" s="69" t="s">
-        <v>123</v>
+      <c r="C44" s="68" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="C45" s="69" t="s">
-        <v>138</v>
+      <c r="C45" s="68" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="2:3">
-      <c r="C46" s="69" t="s">
-        <v>145</v>
+      <c r="C46" s="68" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="69" t="s">
-        <v>120</v>
+        <v>132</v>
+      </c>
+      <c r="C47" s="68" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="2:3">
-      <c r="C48" s="69" t="s">
-        <v>139</v>
+      <c r="C48" s="68" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="3:3">
-      <c r="C49" s="69" t="s">
-        <v>148</v>
+      <c r="C49" s="68" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="3:3">
-      <c r="C51" s="69" t="s">
-        <v>147</v>
+      <c r="C51" s="68" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="3:3">
-      <c r="C52" s="69" t="s">
-        <v>140</v>
+      <c r="C52" s="68" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="3:3">
-      <c r="C53" s="69" t="s">
-        <v>145</v>
+      <c r="C53" s="68" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/IG/7日版/AI Native-提案_IG.xlsx
+++ b/IG/7日版/AI Native-提案_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594AD665-5B04-4BEF-8C5D-A521CBA74553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9AB3B1-DBBF-4F3C-81E3-679E4ECA0287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（3日）" sheetId="33" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（3日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="162">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -798,10 +798,6 @@
     <rPh sb="25" eb="27">
       <t>ブンセキセツメイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ー</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1090,85 +1086,12 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>演習内容の説明</t>
-    <rPh sb="0" eb="2">
-      <t>エンシュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>提案の実施</t>
     <rPh sb="0" eb="2">
       <t>テイアン</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>ジッシ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案の実施の説明</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案の実施</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案テーマの検討</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案テーマの意見交換</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>イケンコウカン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案内容の具体化</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>グタイカ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案テーマの調査</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>チョウサ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1277,59 +1200,6 @@
     </rPh>
     <rPh sb="45" eb="47">
       <t>テイアン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案資料の作成</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シリョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案の改善</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カイゼン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発表順の決定</t>
-    <rPh sb="0" eb="2">
-      <t>ハッピョウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案のフィードバック</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>フィードバック内容の整理</t>
-    <rPh sb="7" eb="9">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セイリ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1427,85 +1297,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>提案資料の作成</t>
-    <rPh sb="5" eb="7">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案資料の提出</t>
-    <rPh sb="5" eb="7">
-      <t>テイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案資料の修正</t>
-    <rPh sb="5" eb="7">
-      <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案資料の確認</t>
-    <rPh sb="5" eb="7">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>提案資料について</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">提案の実施の流れについて説明する。
-■手順
-1. フィードバック内容の整理
-2. 提案資料の修正
-3. 提案資料の確認
-4. 提案資料の提出
-5. 最終発表の準備
-</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>セイリ</t>
-    </rPh>
-    <rPh sb="42" eb="46">
-      <t>テイアンシリョウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>シリョウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>テイシュツ</t>
-    </rPh>
-    <rPh sb="75" eb="79">
-      <t>サイシュウハッピョウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>ジュンビ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1654,20 +1446,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>演習の全体像</t>
-    <rPh sb="0" eb="2">
-      <t>エンシュウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>ゼンタイゾウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>全体像について</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">全体像について説明する。
 ■手順
 1. 提案資料の作成
@@ -1698,10 +1476,6 @@
     <rPh sb="44" eb="46">
       <t>カイゼン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案資料の提出ついて</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1770,6 +1544,232 @@
 　科目の位置づけや目的、全体の説明</t>
     <rPh sb="1" eb="3">
       <t>キョウザイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>研修の全体像について</t>
+    <rPh sb="0" eb="2">
+      <t>ケンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>研修の全体像</t>
+    <rPh sb="0" eb="2">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ゼンタイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の提出について</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の作成について</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の実施について</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の改善について</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提案の改善の流れについて説明する。
+■手順
+1. フィードバック内容の整理
+2. 提案資料の修正
+3. 提案資料の確認
+4. 提案資料の提出
+5. 最終発表の準備
+</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="42" eb="46">
+      <t>テイアンシリョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="75" eb="79">
+      <t>サイシュウハッピョウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>グループ内で提案を実施する。</t>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマを検討し、グループ内でフィードバックをもらう。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案内容の調査 ～ 提案資料の提出</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の改善 ～ 提案資料の提出</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマの検討 ～ 意見交換</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウカン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料を作成し、所定の場所に資料を提出する。</t>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フィードバック内容を整理し、優先度を考慮して、提案資料を改善し、所定の場所に資料を提出する。</t>
+    <rPh sb="32" eb="34">
+      <t>ショテイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>最終発表の準備をする。</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウハッピョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジュンビ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2219,7 +2219,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2532,6 +2532,15 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2541,6 +2550,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2560,22 +2578,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3064,7 +3076,7 @@
         <v>0.40625</v>
       </c>
       <c r="G11" s="77" t="str">
-        <f>master!B42</f>
+        <f>master!C40</f>
         <v>提案の実施</v>
       </c>
     </row>
@@ -3127,7 +3139,7 @@
       </c>
       <c r="C16" s="89" t="str">
         <f>master!B32</f>
-        <v>演習の全体像</v>
+        <v>研修の全体像</v>
       </c>
       <c r="D16" s="82"/>
       <c r="E16" s="78"/>
@@ -3137,10 +3149,7 @@
     <row r="17" spans="1:8">
       <c r="A17" s="48"/>
       <c r="B17" s="54"/>
-      <c r="C17" s="85" t="str">
-        <f>master!B35</f>
-        <v>提案資料の作成</v>
-      </c>
+      <c r="C17" s="76"/>
       <c r="D17" s="82"/>
       <c r="E17" s="78"/>
       <c r="F17" s="54"/>
@@ -3149,7 +3158,10 @@
     <row r="18" spans="1:8">
       <c r="A18" s="48"/>
       <c r="B18" s="54"/>
-      <c r="C18" s="85"/>
+      <c r="C18" s="85" t="str">
+        <f>master!C38</f>
+        <v>提案テーマの検討 ～ 意見交換</v>
+      </c>
       <c r="D18" s="82"/>
       <c r="E18" s="78"/>
       <c r="F18" s="54"/>
@@ -3257,7 +3269,10 @@
       <c r="B26" s="36">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="77"/>
+      <c r="C26" s="77" t="str">
+        <f>master!C39</f>
+        <v>提案内容の調査 ～ 提案資料の提出</v>
+      </c>
       <c r="D26" s="36">
         <v>0.5625</v>
       </c>
@@ -3266,8 +3281,8 @@
         <v>0.5625</v>
       </c>
       <c r="G26" s="77" t="str">
-        <f>master!B47</f>
-        <v>提案の改善</v>
+        <f>master!C41</f>
+        <v>提案の改善 ～ 提案資料の提出</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3400,8 +3415,8 @@
       <c r="C39" s="78"/>
       <c r="D39" s="38"/>
       <c r="E39" s="78"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="78"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="76"/>
       <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8">
@@ -3412,8 +3427,13 @@
       <c r="C40" s="78"/>
       <c r="D40" s="38"/>
       <c r="E40" s="78"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="76"/>
+      <c r="F40" s="122">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="G40" s="76" t="str">
+        <f>master!C42</f>
+        <v>最終発表の準備</v>
+      </c>
       <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8">
@@ -3426,7 +3446,7 @@
         <v>0.71875</v>
       </c>
       <c r="G41" s="81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H41" s="49"/>
     </row>
@@ -3580,7 +3600,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>19</v>
@@ -3643,10 +3663,10 @@
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E12" s="96"/>
       <c r="F12" s="96"/>
@@ -3667,15 +3687,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="96" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="96"/>
       <c r="F13" s="96"/>
       <c r="G13" s="79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="45" t="s">
@@ -3691,15 +3711,15 @@
       <c r="A14" s="10"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="96" t="s">
         <v>114</v>
-      </c>
-      <c r="D14" s="96" t="s">
-        <v>115</v>
       </c>
       <c r="E14" s="96"/>
       <c r="F14" s="96"/>
       <c r="G14" s="79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="45" t="s">
@@ -3748,7 +3768,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N61"/>
+  <dimension ref="A2:N62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3760,7 +3780,7 @@
     <col min="7" max="7" width="9.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="38.44140625" style="10" customWidth="1"/>
     <col min="12" max="12" width="6.44140625" style="1" customWidth="1"/>
     <col min="13" max="13" width="38.44140625" style="1" customWidth="1"/>
@@ -3814,16 +3834,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="112"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="112"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -3865,7 +3885,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>19</v>
@@ -3887,7 +3907,7 @@
         <v>34</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D9" s="41" t="s">
         <v>19</v>
@@ -3909,7 +3929,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D10" s="41" t="s">
         <v>19</v>
@@ -3945,10 +3965,10 @@
       <c r="H12" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="110" t="s">
+      <c r="I12" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="111"/>
+      <c r="J12" s="117"/>
       <c r="K12" s="97" t="s">
         <v>32</v>
       </c>
@@ -3986,11 +4006,11 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D14" s="107" t="s">
+      <c r="D14" s="113" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="108"/>
-      <c r="F14" s="109"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="115"/>
       <c r="G14" s="46" t="s">
         <v>77</v>
       </c>
@@ -3999,7 +4019,7 @@
         <v>24</v>
       </c>
       <c r="J14" s="42">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K14" s="39"/>
       <c r="L14" s="6"/>
@@ -4008,7 +4028,7 @@
     </row>
     <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="116" t="str">
+      <c r="B15" s="110" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4016,11 +4036,11 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D15" s="107" t="s">
+      <c r="D15" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="108"/>
-      <c r="F15" s="109"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
       <c r="G15" s="46" t="s">
         <v>77</v>
       </c>
@@ -4029,7 +4049,7 @@
         <v>24</v>
       </c>
       <c r="J15" s="42">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K15" s="39"/>
       <c r="L15" s="6"/>
@@ -4038,25 +4058,25 @@
     </row>
     <row r="16" spans="1:14" ht="163.80000000000001">
       <c r="A16" s="11"/>
-      <c r="B16" s="117"/>
+      <c r="B16" s="111"/>
       <c r="C16" s="46" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D16" s="107" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="108"/>
-      <c r="F16" s="109"/>
+      <c r="D16" s="113" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="44" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="42">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K16" s="39"/>
       <c r="L16" s="6"/>
@@ -4065,16 +4085,16 @@
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="117"/>
+      <c r="B17" s="111"/>
       <c r="C17" s="46" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D17" s="107" t="s">
+      <c r="D17" s="113" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
       <c r="G17" s="46" t="s">
         <v>35</v>
       </c>
@@ -4083,7 +4103,7 @@
         <v>24</v>
       </c>
       <c r="J17" s="42">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K17" s="39"/>
       <c r="L17" s="6"/>
@@ -4092,16 +4112,16 @@
     </row>
     <row r="18" spans="1:14" ht="151.19999999999999">
       <c r="A18" s="11"/>
-      <c r="B18" s="117"/>
+      <c r="B18" s="111"/>
       <c r="C18" s="46" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D18" s="107" t="s">
+      <c r="D18" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="108"/>
-      <c r="F18" s="109"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="115"/>
       <c r="G18" s="46" t="s">
         <v>41</v>
       </c>
@@ -4119,16 +4139,16 @@
     </row>
     <row r="19" spans="1:14" ht="252">
       <c r="A19" s="11"/>
-      <c r="B19" s="117"/>
+      <c r="B19" s="111"/>
       <c r="C19" s="46" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D19" s="107" t="s">
+      <c r="D19" s="113" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="108"/>
-      <c r="F19" s="109"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
       <c r="G19" s="46" t="s">
         <v>43</v>
       </c>
@@ -4137,7 +4157,7 @@
         <v>24</v>
       </c>
       <c r="J19" s="42">
-        <v>0</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K19" s="39"/>
       <c r="L19" s="6"/>
@@ -4146,16 +4166,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="117"/>
+      <c r="B20" s="111"/>
       <c r="C20" s="46" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D20" s="107" t="s">
+      <c r="D20" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="108"/>
-      <c r="F20" s="109"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="46" t="s">
         <v>42</v>
       </c>
@@ -4164,7 +4184,7 @@
         <v>24</v>
       </c>
       <c r="J20" s="42">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="6"/>
@@ -4173,16 +4193,16 @@
     </row>
     <row r="21" spans="1:14" ht="63">
       <c r="A21" s="11"/>
-      <c r="B21" s="117"/>
+      <c r="B21" s="111"/>
       <c r="C21" s="46" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D21" s="107" t="s">
+      <c r="D21" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="46" t="s">
         <v>77</v>
       </c>
@@ -4200,16 +4220,16 @@
     </row>
     <row r="22" spans="1:14" ht="75.599999999999994">
       <c r="A22" s="11"/>
-      <c r="B22" s="117"/>
+      <c r="B22" s="111"/>
       <c r="C22" s="46" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D22" s="107" t="s">
+      <c r="D22" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="115"/>
       <c r="G22" s="46" t="s">
         <v>36</v>
       </c>
@@ -4227,16 +4247,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="117"/>
+      <c r="B23" s="111"/>
       <c r="C23" s="46" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D23" s="107" t="s">
+      <c r="D23" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="115"/>
       <c r="G23" s="46" t="s">
         <v>36</v>
       </c>
@@ -4245,7 +4265,7 @@
         <v>24</v>
       </c>
       <c r="J23" s="42">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K23" s="39"/>
       <c r="L23" s="6"/>
@@ -4254,16 +4274,16 @@
     </row>
     <row r="24" spans="1:14" ht="113.4">
       <c r="A24" s="11"/>
-      <c r="B24" s="117"/>
+      <c r="B24" s="111"/>
       <c r="C24" s="46" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D24" s="107" t="s">
+      <c r="D24" s="113" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="46" t="s">
         <v>37</v>
       </c>
@@ -4281,16 +4301,16 @@
     </row>
     <row r="25" spans="1:14" ht="88.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="117"/>
+      <c r="B25" s="111"/>
       <c r="C25" s="46" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D25" s="107" t="s">
+      <c r="D25" s="113" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="46" t="s">
         <v>38</v>
       </c>
@@ -4308,16 +4328,16 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="118"/>
+      <c r="B26" s="112"/>
       <c r="C26" s="46" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D26" s="107" t="s">
+      <c r="D26" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="115"/>
       <c r="G26" s="46" t="s">
         <v>37</v>
       </c>
@@ -4335,7 +4355,7 @@
     </row>
     <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="116" t="str">
+      <c r="B27" s="110" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4343,11 +4363,11 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D27" s="107" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109"/>
+      <c r="D27" s="113" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="114"/>
+      <c r="F27" s="115"/>
       <c r="G27" s="46" t="s">
         <v>92</v>
       </c>
@@ -4365,16 +4385,16 @@
     </row>
     <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="117"/>
+      <c r="B28" s="111"/>
       <c r="C28" s="46" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D28" s="107" t="s">
+      <c r="D28" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="46" t="s">
         <v>73</v>
       </c>
@@ -4392,16 +4412,16 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="117"/>
+      <c r="B29" s="111"/>
       <c r="C29" s="46" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D29" s="107" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109"/>
+      <c r="D29" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
       <c r="G29" s="46" t="s">
         <v>73</v>
       </c>
@@ -4419,16 +4439,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="117"/>
+      <c r="B30" s="111"/>
       <c r="C30" s="46" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D30" s="107" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109"/>
+      <c r="D30" s="113" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="114"/>
+      <c r="F30" s="115"/>
       <c r="G30" s="46" t="s">
         <v>73</v>
       </c>
@@ -4446,16 +4466,16 @@
     </row>
     <row r="31" spans="1:14" ht="63">
       <c r="A31" s="11"/>
-      <c r="B31" s="117"/>
+      <c r="B31" s="111"/>
       <c r="C31" s="46" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D31" s="107" t="s">
+      <c r="D31" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="108"/>
-      <c r="F31" s="109"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="115"/>
       <c r="G31" s="46" t="s">
         <v>93</v>
       </c>
@@ -4473,16 +4493,16 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="117"/>
+      <c r="B32" s="111"/>
       <c r="C32" s="46" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D32" s="107" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
+      <c r="D32" s="113" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="114"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="46" t="s">
         <v>92</v>
       </c>
@@ -4500,16 +4520,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="117"/>
+      <c r="B33" s="111"/>
       <c r="C33" s="46" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D33" s="107" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
+      <c r="D33" s="113" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="114"/>
+      <c r="F33" s="115"/>
       <c r="G33" s="46" t="s">
         <v>92</v>
       </c>
@@ -4527,16 +4547,16 @@
     </row>
     <row r="34" spans="1:14" ht="63">
       <c r="A34" s="11"/>
-      <c r="B34" s="117"/>
+      <c r="B34" s="111"/>
       <c r="C34" s="46" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D34" s="107" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="108"/>
-      <c r="F34" s="109"/>
+      <c r="D34" s="113" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
       <c r="G34" s="46" t="s">
         <v>93</v>
       </c>
@@ -4554,16 +4574,16 @@
     </row>
     <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="117"/>
+      <c r="B35" s="111"/>
       <c r="C35" s="46" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D35" s="107" t="s">
+      <c r="D35" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="108"/>
-      <c r="F35" s="109"/>
+      <c r="E35" s="114"/>
+      <c r="F35" s="115"/>
       <c r="G35" s="46" t="s">
         <v>73</v>
       </c>
@@ -4581,16 +4601,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="117"/>
+      <c r="B36" s="111"/>
       <c r="C36" s="46" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D36" s="107" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="108"/>
-      <c r="F36" s="109"/>
+      <c r="D36" s="113" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="114"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="46" t="s">
         <v>92</v>
       </c>
@@ -4608,16 +4628,16 @@
     </row>
     <row r="37" spans="1:14" ht="63">
       <c r="A37" s="11"/>
-      <c r="B37" s="117"/>
+      <c r="B37" s="111"/>
       <c r="C37" s="46" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D37" s="107" t="s">
+      <c r="D37" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="E37" s="108"/>
-      <c r="F37" s="109"/>
+      <c r="E37" s="114"/>
+      <c r="F37" s="115"/>
       <c r="G37" s="46" t="s">
         <v>93</v>
       </c>
@@ -4635,16 +4655,16 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="117"/>
+      <c r="B38" s="111"/>
       <c r="C38" s="46" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D38" s="107" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="108"/>
-      <c r="F38" s="109"/>
+      <c r="D38" s="113" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="114"/>
+      <c r="F38" s="115"/>
       <c r="G38" s="46" t="s">
         <v>93</v>
       </c>
@@ -4662,16 +4682,16 @@
     </row>
     <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="118"/>
+      <c r="B39" s="112"/>
       <c r="C39" s="46" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D39" s="107" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="108"/>
-      <c r="F39" s="109"/>
+      <c r="D39" s="113" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
       <c r="G39" s="46" t="s">
         <v>92</v>
       </c>
@@ -4689,21 +4709,21 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="113" t="str">
+      <c r="B40" s="104" t="str">
         <f>master!B32</f>
-        <v>演習の全体像</v>
+        <v>研修の全体像</v>
       </c>
       <c r="C40" s="63" t="str">
         <f>master!C32</f>
-        <v>全体像について</v>
-      </c>
-      <c r="D40" s="104" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" s="105"/>
-      <c r="F40" s="106"/>
+        <v>研修の全体像について</v>
+      </c>
+      <c r="D40" s="107" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="108"/>
+      <c r="F40" s="109"/>
       <c r="G40" s="63" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H40" s="64"/>
       <c r="I40" s="65" t="s">
@@ -4719,16 +4739,16 @@
     </row>
     <row r="41" spans="1:14" ht="138.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="114"/>
+      <c r="B41" s="105"/>
       <c r="C41" s="63" t="str">
         <f>master!C33</f>
         <v>提案資料について</v>
       </c>
-      <c r="D41" s="104" t="s">
-        <v>161</v>
-      </c>
-      <c r="E41" s="105"/>
-      <c r="F41" s="106"/>
+      <c r="D41" s="107" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" s="108"/>
+      <c r="F41" s="109"/>
       <c r="G41" s="63" t="s">
         <v>75</v>
       </c>
@@ -4746,25 +4766,25 @@
     </row>
     <row r="42" spans="1:14" ht="126">
       <c r="A42" s="11"/>
-      <c r="B42" s="115"/>
+      <c r="B42" s="105"/>
       <c r="C42" s="63" t="str">
         <f>master!C34</f>
-        <v>提案資料の提出ついて</v>
-      </c>
-      <c r="D42" s="104" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="105"/>
-      <c r="F42" s="106"/>
+        <v>提案資料の提出について</v>
+      </c>
+      <c r="D42" s="107" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="108"/>
+      <c r="F42" s="109"/>
       <c r="G42" s="63" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="H42" s="63"/>
       <c r="I42" s="65" t="s">
         <v>24</v>
       </c>
       <c r="J42" s="66">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K42" s="67"/>
       <c r="L42" s="6"/>
@@ -4773,21 +4793,18 @@
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="113" t="str">
-        <f>master!B35</f>
-        <v>提案資料の作成</v>
-      </c>
-      <c r="C43" s="63" t="str">
+      <c r="B43" s="105"/>
+      <c r="C43" s="119" t="str">
         <f>master!C35</f>
-        <v>提案テーマの検討</v>
-      </c>
-      <c r="D43" s="104" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="105"/>
-      <c r="F43" s="106"/>
+        <v>提案資料の作成について</v>
+      </c>
+      <c r="D43" s="107" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="108"/>
+      <c r="F43" s="109"/>
       <c r="G43" s="63" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H43" s="64"/>
       <c r="I43" s="65" t="s">
@@ -4803,16 +4820,13 @@
     </row>
     <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="63" t="str">
-        <f>master!C36</f>
-        <v>提案テーマの意見交換</v>
-      </c>
-      <c r="D44" s="104" t="s">
-        <v>138</v>
-      </c>
-      <c r="E44" s="105"/>
-      <c r="F44" s="106"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="120"/>
+      <c r="D44" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="108"/>
+      <c r="F44" s="109"/>
       <c r="G44" s="63" t="s">
         <v>75</v>
       </c>
@@ -4830,18 +4844,15 @@
     </row>
     <row r="45" spans="1:14" ht="75.599999999999994">
       <c r="A45" s="11"/>
-      <c r="B45" s="114"/>
-      <c r="C45" s="63" t="str">
-        <f>master!C37</f>
-        <v>提案テーマの調査</v>
-      </c>
-      <c r="D45" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="105"/>
-      <c r="F45" s="106"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="120"/>
+      <c r="D45" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" s="108"/>
+      <c r="F45" s="109"/>
       <c r="G45" s="63" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H45" s="64"/>
       <c r="I45" s="65" t="s">
@@ -4857,18 +4868,15 @@
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="114"/>
-      <c r="C46" s="63" t="str">
-        <f>master!C38</f>
-        <v>提案内容の具体化</v>
-      </c>
-      <c r="D46" s="104" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="105"/>
-      <c r="F46" s="106"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="120"/>
+      <c r="D46" s="107" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
       <c r="G46" s="63" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H46" s="64"/>
       <c r="I46" s="65" t="s">
@@ -4884,18 +4892,15 @@
     </row>
     <row r="47" spans="1:14" ht="151.19999999999999">
       <c r="A47" s="11"/>
-      <c r="B47" s="114"/>
-      <c r="C47" s="63" t="str">
-        <f>master!C39</f>
-        <v>提案資料の作成</v>
-      </c>
-      <c r="D47" s="104" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="105"/>
-      <c r="F47" s="106"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="120"/>
+      <c r="D47" s="107" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" s="108"/>
+      <c r="F47" s="109"/>
       <c r="G47" s="63" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H47" s="64"/>
       <c r="I47" s="65" t="s">
@@ -4911,16 +4916,13 @@
     </row>
     <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="114"/>
-      <c r="C48" s="63" t="str">
-        <f>master!C40</f>
-        <v>提案資料の提出</v>
-      </c>
-      <c r="D48" s="104" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" s="105"/>
-      <c r="F48" s="106"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="121"/>
+      <c r="D48" s="107" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="108"/>
+      <c r="F48" s="109"/>
       <c r="G48" s="63" t="s">
         <v>76</v>
       </c>
@@ -4936,48 +4938,44 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="25.2">
+    <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="114"/>
-      <c r="C49" s="63" t="str">
-        <f>master!C41</f>
-        <v>演習の実施</v>
-      </c>
-      <c r="D49" s="104"/>
-      <c r="E49" s="105"/>
-      <c r="F49" s="106"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="119" t="str">
+        <f>master!C36</f>
+        <v>提案の実施について</v>
+      </c>
+      <c r="D49" s="107" t="s">
+        <v>122</v>
+      </c>
+      <c r="E49" s="108"/>
+      <c r="F49" s="109"/>
       <c r="G49" s="63" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="H49" s="64"/>
       <c r="I49" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="66" t="s">
-        <v>96</v>
+      <c r="J49" s="66">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K49" s="67"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="88.2">
+    <row r="50" spans="1:14" ht="25.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="113" t="str">
-        <f>master!B42</f>
-        <v>提案の実施</v>
-      </c>
-      <c r="C50" s="63" t="str">
-        <f>master!C42</f>
-        <v>提案の実施の説明</v>
-      </c>
-      <c r="D50" s="104" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" s="105"/>
-      <c r="F50" s="106"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="120"/>
+      <c r="D50" s="107" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="108"/>
+      <c r="F50" s="109"/>
       <c r="G50" s="63" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="H50" s="64"/>
       <c r="I50" s="65" t="s">
@@ -4993,16 +4991,13 @@
     </row>
     <row r="51" spans="1:14" ht="25.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="114"/>
-      <c r="C51" s="63" t="str">
-        <f>master!C43</f>
-        <v>発表順の決定</v>
-      </c>
-      <c r="D51" s="104" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="105"/>
-      <c r="F51" s="106"/>
+      <c r="B51" s="105"/>
+      <c r="C51" s="120"/>
+      <c r="D51" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="108"/>
+      <c r="F51" s="109"/>
       <c r="G51" s="63" t="s">
         <v>76</v>
       </c>
@@ -5020,16 +5015,13 @@
     </row>
     <row r="52" spans="1:14" ht="25.2">
       <c r="A52" s="11"/>
-      <c r="B52" s="114"/>
-      <c r="C52" s="63" t="str">
-        <f>master!C44</f>
-        <v>提案の実施</v>
-      </c>
-      <c r="D52" s="104" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" s="105"/>
-      <c r="F52" s="106"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="121"/>
+      <c r="D52" s="107" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="108"/>
+      <c r="F52" s="109"/>
       <c r="G52" s="63" t="s">
         <v>76</v>
       </c>
@@ -5045,20 +5037,20 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="25.2">
+    <row r="53" spans="1:14" ht="113.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="114"/>
-      <c r="C53" s="63" t="str">
-        <f>master!C45</f>
-        <v>提案のフィードバック</v>
-      </c>
-      <c r="D53" s="104" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" s="105"/>
-      <c r="F53" s="106"/>
+      <c r="B53" s="105"/>
+      <c r="C53" s="119" t="str">
+        <f>master!C37</f>
+        <v>提案の改善について</v>
+      </c>
+      <c r="D53" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="108"/>
+      <c r="F53" s="109"/>
       <c r="G53" s="63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H53" s="64"/>
       <c r="I53" s="65" t="s">
@@ -5074,14 +5066,13 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="115"/>
-      <c r="C54" s="63" t="str">
-        <f>master!C46</f>
-        <v>演習の実施</v>
-      </c>
-      <c r="D54" s="104"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="106"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="107" t="s">
+        <v>132</v>
+      </c>
+      <c r="E54" s="108"/>
+      <c r="F54" s="109"/>
       <c r="G54" s="63" t="s">
         <v>76</v>
       </c>
@@ -5089,31 +5080,25 @@
       <c r="I54" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="66" t="s">
-        <v>96</v>
+      <c r="J54" s="66">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K54" s="67"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:14" ht="113.4">
+    <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="113" t="str">
-        <f>master!B47</f>
-        <v>提案の改善</v>
-      </c>
-      <c r="C55" s="63" t="str">
-        <f>master!C47</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D55" s="104" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" s="105"/>
-      <c r="F55" s="106"/>
+      <c r="B55" s="105"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="107" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="108"/>
+      <c r="F55" s="109"/>
       <c r="G55" s="63" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H55" s="64"/>
       <c r="I55" s="65" t="s">
@@ -5129,16 +5114,13 @@
     </row>
     <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="114"/>
-      <c r="C56" s="63" t="str">
-        <f>master!C48</f>
-        <v>フィードバック内容の整理</v>
-      </c>
-      <c r="D56" s="104" t="s">
-        <v>150</v>
-      </c>
-      <c r="E56" s="105"/>
-      <c r="F56" s="106"/>
+      <c r="B56" s="105"/>
+      <c r="C56" s="120"/>
+      <c r="D56" s="107" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" s="108"/>
+      <c r="F56" s="109"/>
       <c r="G56" s="63" t="s">
         <v>76</v>
       </c>
@@ -5154,20 +5136,17 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="25.2">
+    <row r="57" spans="1:14" ht="37.799999999999997">
       <c r="A57" s="11"/>
-      <c r="B57" s="114"/>
-      <c r="C57" s="63" t="str">
-        <f>master!C49</f>
-        <v>提案資料の修正</v>
-      </c>
-      <c r="D57" s="104" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" s="105"/>
-      <c r="F57" s="106"/>
+      <c r="B57" s="106"/>
+      <c r="C57" s="121"/>
+      <c r="D57" s="107" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" s="108"/>
+      <c r="F57" s="109"/>
       <c r="G57" s="63" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="H57" s="64"/>
       <c r="I57" s="65" t="s">
@@ -5181,18 +5160,21 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="25.2">
+    <row r="58" spans="1:14" ht="26.4" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="114"/>
+      <c r="B58" s="104" t="str">
+        <f>master!B38</f>
+        <v>演習の実施</v>
+      </c>
       <c r="C58" s="63" t="str">
-        <f>master!C50</f>
-        <v>提案資料の確認</v>
-      </c>
-      <c r="D58" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="105"/>
-      <c r="F58" s="106"/>
+        <f>master!C38</f>
+        <v>提案テーマの検討 ～ 意見交換</v>
+      </c>
+      <c r="D58" s="107" t="s">
+        <v>155</v>
+      </c>
+      <c r="E58" s="108"/>
+      <c r="F58" s="109"/>
       <c r="G58" s="63" t="s">
         <v>76</v>
       </c>
@@ -5201,34 +5183,34 @@
         <v>24</v>
       </c>
       <c r="J58" s="66">
-        <v>6.9444444444444447E-4</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="K58" s="67"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="37.799999999999997">
+    <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="114"/>
+      <c r="B59" s="105"/>
       <c r="C59" s="63" t="str">
-        <f>master!C51</f>
-        <v>提案資料の提出</v>
-      </c>
-      <c r="D59" s="104" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" s="105"/>
-      <c r="F59" s="106"/>
+        <f>master!C39</f>
+        <v>提案内容の調査 ～ 提案資料の提出</v>
+      </c>
+      <c r="D59" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" s="108"/>
+      <c r="F59" s="109"/>
       <c r="G59" s="63" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="H59" s="64"/>
       <c r="I59" s="65" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="66">
-        <v>6.9444444444444447E-4</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="K59" s="67"/>
       <c r="L59" s="6"/>
@@ -5237,14 +5219,16 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="114"/>
+      <c r="B60" s="105"/>
       <c r="C60" s="63" t="str">
-        <f>master!C52</f>
-        <v>最終発表の準備</v>
-      </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="106"/>
+        <f>master!C40</f>
+        <v>提案の実施</v>
+      </c>
+      <c r="D60" s="107" t="s">
+        <v>154</v>
+      </c>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
       <c r="G60" s="63" t="s">
         <v>76</v>
       </c>
@@ -5253,7 +5237,7 @@
         <v>24</v>
       </c>
       <c r="J60" s="66">
-        <v>6.9444444444444447E-4</v>
+        <v>0.125</v>
       </c>
       <c r="K60" s="67"/>
       <c r="L60" s="6"/>
@@ -5262,14 +5246,16 @@
     </row>
     <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="115"/>
+      <c r="B61" s="106"/>
       <c r="C61" s="63" t="str">
-        <f>master!C53</f>
-        <v>演習の実施</v>
-      </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="106"/>
+        <f>master!C41</f>
+        <v>提案の改善 ～ 提案資料の提出</v>
+      </c>
+      <c r="D61" s="107" t="s">
+        <v>160</v>
+      </c>
+      <c r="E61" s="108"/>
+      <c r="F61" s="109"/>
       <c r="G61" s="63" t="s">
         <v>76</v>
       </c>
@@ -5277,23 +5263,86 @@
       <c r="I61" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J61" s="66" t="s">
-        <v>96</v>
+      <c r="J61" s="66">
+        <v>0.125</v>
       </c>
       <c r="K61" s="67"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
+    <row r="62" spans="1:14" ht="25.2">
+      <c r="A62" s="11"/>
+      <c r="B62" s="63" t="str">
+        <f>master!B42</f>
+        <v>最終発表の準備</v>
+      </c>
+      <c r="C62" s="63" t="str">
+        <f>master!C42</f>
+        <v>最終発表の準備</v>
+      </c>
+      <c r="D62" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="E62" s="108"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H62" s="64"/>
+      <c r="I62" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="66">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K62" s="67"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="D60:F60"/>
+  <mergeCells count="63">
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="B55:B61"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="B15:B26"/>
     <mergeCell ref="D27:F27"/>
@@ -5309,48 +5358,14 @@
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B43:B49"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D61:F61"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D57:F57"/>
     <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B40:B57"/>
+    <mergeCell ref="D60:F60"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5363,7 +5378,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H14:H41 H43:H61</xm:sqref>
+          <xm:sqref>H14:H41 H43:H62</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5383,7 +5398,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -5478,10 +5493,10 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="2:3">
@@ -5550,125 +5565,97 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" s="68" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" s="68" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" t="s">
-        <v>131</v>
-      </c>
       <c r="C35" s="68" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" s="68" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" s="68" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="2:3">
-      <c r="C38" t="s">
-        <v>122</v>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="C39" t="s">
-        <v>142</v>
+      <c r="C39" s="68" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="C40" t="s">
-        <v>143</v>
+      <c r="C40" s="68" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" s="68" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="68" t="s">
-        <v>118</v>
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" s="68" t="s">
-        <v>133</v>
-      </c>
+      <c r="C43" s="68"/>
     </row>
     <row r="44" spans="2:3">
-      <c r="C44" s="68" t="s">
-        <v>119</v>
-      </c>
+      <c r="C44" s="68"/>
     </row>
     <row r="45" spans="2:3">
-      <c r="C45" s="68" t="s">
-        <v>134</v>
-      </c>
+      <c r="C45" s="68"/>
     </row>
     <row r="46" spans="2:3">
-      <c r="C46" s="68" t="s">
-        <v>141</v>
-      </c>
+      <c r="C46" s="68"/>
     </row>
     <row r="47" spans="2:3">
-      <c r="B47" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" s="68" t="s">
-        <v>116</v>
-      </c>
+      <c r="C47" s="68"/>
     </row>
     <row r="48" spans="2:3">
-      <c r="C48" s="68" t="s">
-        <v>135</v>
-      </c>
+      <c r="C48" s="68"/>
     </row>
     <row r="49" spans="3:3">
-      <c r="C49" s="68" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" t="s">
-        <v>145</v>
-      </c>
+      <c r="C49" s="68"/>
     </row>
     <row r="51" spans="3:3">
-      <c r="C51" s="68" t="s">
-        <v>143</v>
-      </c>
+      <c r="C51" s="68"/>
     </row>
     <row r="52" spans="3:3">
-      <c r="C52" s="68" t="s">
-        <v>136</v>
-      </c>
+      <c r="C52" s="68"/>
     </row>
     <row r="53" spans="3:3">
-      <c r="C53" s="68" t="s">
-        <v>141</v>
-      </c>
+      <c r="C53" s="68"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
